--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120256209</v>
+        <v>120256073</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -722,7 +723,7 @@
         <v>339403</v>
       </c>
       <c r="R2" t="n">
-        <v>6433219</v>
+        <v>6433234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,6 +769,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120256522</v>
+        <v>120256264</v>
       </c>
       <c r="B3" t="n">
-        <v>96631</v>
+        <v>96198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +800,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2617</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,8 +821,16 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -830,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339437</v>
+        <v>339412</v>
       </c>
       <c r="R3" t="n">
-        <v>6433270</v>
+        <v>6433188</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120256264</v>
+        <v>120253314</v>
       </c>
       <c r="B4" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,12 +943,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -950,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339412</v>
+        <v>339450</v>
       </c>
       <c r="R4" t="n">
-        <v>6433188</v>
+        <v>6433265</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,11 +996,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1026,7 @@
         <v>120256132</v>
       </c>
       <c r="B5" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253580</v>
+        <v>120256522</v>
       </c>
       <c r="B6" t="n">
-        <v>57679</v>
+        <v>96654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,39 +1155,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2617</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1190,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339432</v>
+        <v>339437</v>
       </c>
       <c r="R6" t="n">
-        <v>6433269</v>
+        <v>6433270</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,6 +1236,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1257,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120256073</v>
+        <v>120256209</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,29 +1267,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1305,7 +1302,7 @@
         <v>339403</v>
       </c>
       <c r="R7" t="n">
-        <v>6433234</v>
+        <v>6433219</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1348,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1373,7 +1369,7 @@
         <v>120256381</v>
       </c>
       <c r="B8" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1602,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253314</v>
+        <v>120253580</v>
       </c>
       <c r="B10" t="n">
-        <v>96175</v>
+        <v>57689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,35 +1614,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1654,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339450</v>
+        <v>339432</v>
       </c>
       <c r="R10" t="n">
-        <v>6433265</v>
+        <v>6433269</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1692,13 +1688,17 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>120253305</v>
       </c>
       <c r="B11" t="n">
-        <v>96175</v>
+        <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>120255941</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120256073</v>
+        <v>120256264</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>96198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339403</v>
+        <v>339412</v>
       </c>
       <c r="R2" t="n">
-        <v>6433234</v>
+        <v>6433188</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120256264</v>
+        <v>120256073</v>
       </c>
       <c r="B3" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339412</v>
+        <v>339403</v>
       </c>
       <c r="R3" t="n">
-        <v>6433188</v>
+        <v>6433234</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1946,6 +1946,123 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120392076</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mickelsdamm, OSO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>339403</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433234</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnag på samma granhögstubbe som bronshjon.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120256264</v>
+        <v>120253314</v>
       </c>
       <c r="B2" t="n">
         <v>96198</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339412</v>
+        <v>339450</v>
       </c>
       <c r="R2" t="n">
-        <v>6433188</v>
+        <v>6433265</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120256073</v>
+        <v>120253580</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,28 +806,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339403</v>
+        <v>339432</v>
       </c>
       <c r="R3" t="n">
-        <v>6433234</v>
+        <v>6433269</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120253314</v>
+        <v>120256264</v>
       </c>
       <c r="B4" t="n">
         <v>96198</v>
@@ -943,12 +944,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -960,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339450</v>
+        <v>339412</v>
       </c>
       <c r="R4" t="n">
-        <v>6433265</v>
+        <v>6433188</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,6 +997,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120256132</v>
+        <v>120256522</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>96654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,20 +1041,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2617</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1056,16 +1062,8 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R5" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,7 +1113,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120256522</v>
+        <v>120253305</v>
       </c>
       <c r="B6" t="n">
-        <v>96654</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,20 +1153,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2617</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1176,8 +1174,16 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1187,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339437</v>
+        <v>339460</v>
       </c>
       <c r="R6" t="n">
-        <v>6433270</v>
+        <v>6433267</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120256209</v>
+        <v>120256381</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,31 +1273,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1299,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339403</v>
+        <v>339476</v>
       </c>
       <c r="R7" t="n">
-        <v>6433219</v>
+        <v>6433278</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,17 +1351,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1366,7 +1376,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120256381</v>
+        <v>120256132</v>
       </c>
       <c r="B8" t="n">
         <v>96198</v>
@@ -1401,7 +1411,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1418,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339476</v>
+        <v>339403</v>
       </c>
       <c r="R8" t="n">
-        <v>6433278</v>
+        <v>6433234</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,6 +1464,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253460</v>
+        <v>120256209</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,36 +1508,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1530,10 +1540,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339437</v>
+        <v>339403</v>
       </c>
       <c r="R9" t="n">
-        <v>6433270</v>
+        <v>6433219</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,7 +1580,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
+          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,7 +1589,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253580</v>
+        <v>120256073</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>5169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,35 +1623,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1650,10 +1652,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339432</v>
+        <v>339403</v>
       </c>
       <c r="R10" t="n">
-        <v>6433269</v>
+        <v>6433234</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1690,7 +1692,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,6 +1701,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1717,10 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120253305</v>
+        <v>120255941</v>
       </c>
       <c r="B11" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,39 +1732,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1769,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339460</v>
+        <v>339403</v>
       </c>
       <c r="R11" t="n">
-        <v>6433267</v>
+        <v>6433234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1809,7 +1804,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
+          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1813,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1837,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120255941</v>
+        <v>120253460</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,31 +1843,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1881,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R12" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1921,7 +1920,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
+          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,6 +1929,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120253314</v>
+        <v>120253305</v>
       </c>
       <c r="B2" t="n">
         <v>96198</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339450</v>
+        <v>339460</v>
       </c>
       <c r="R2" t="n">
-        <v>6433265</v>
+        <v>6433267</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120253580</v>
+        <v>120256522</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>96654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +807,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2617</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339432</v>
+        <v>339437</v>
       </c>
       <c r="R3" t="n">
-        <v>6433269</v>
+        <v>6433270</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120256264</v>
+        <v>120256381</v>
       </c>
       <c r="B4" t="n">
         <v>96198</v>
@@ -944,12 +942,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -961,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339412</v>
+        <v>339476</v>
       </c>
       <c r="R4" t="n">
-        <v>6433188</v>
+        <v>6433278</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,11 +995,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120256522</v>
+        <v>120255941</v>
       </c>
       <c r="B5" t="n">
-        <v>96654</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,31 +1034,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2617</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339437</v>
+        <v>339403</v>
       </c>
       <c r="R5" t="n">
-        <v>6433270</v>
+        <v>6433234</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,7 +1106,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,7 +1115,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253305</v>
+        <v>120253580</v>
       </c>
       <c r="B6" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,35 +1149,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339460</v>
+        <v>339432</v>
       </c>
       <c r="R6" t="n">
-        <v>6433267</v>
+        <v>6433269</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1225,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1234,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1261,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120256381</v>
+        <v>120256073</v>
       </c>
       <c r="B7" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,35 +1268,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1313,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339476</v>
+        <v>339403</v>
       </c>
       <c r="R7" t="n">
-        <v>6433278</v>
+        <v>6433234</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,6 +1333,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120256132</v>
+        <v>120253314</v>
       </c>
       <c r="B8" t="n">
         <v>96198</v>
@@ -1411,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1428,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339403</v>
+        <v>339450</v>
       </c>
       <c r="R8" t="n">
-        <v>6433234</v>
+        <v>6433265</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1464,11 +1453,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1607,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120256073</v>
+        <v>120253460</v>
       </c>
       <c r="B10" t="n">
         <v>5169</v>
@@ -1644,7 +1628,11 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1652,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R10" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1692,7 +1680,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,10 +1708,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120255941</v>
+        <v>120256264</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,31 +1720,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1764,10 +1760,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339403</v>
+        <v>339412</v>
       </c>
       <c r="R11" t="n">
-        <v>6433234</v>
+        <v>6433188</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1804,7 +1800,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,6 +1809,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1831,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253460</v>
+        <v>120256132</v>
       </c>
       <c r="B12" t="n">
-        <v>5169</v>
+        <v>96198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,32 +1844,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339437</v>
+        <v>339403</v>
       </c>
       <c r="R12" t="n">
-        <v>6433270</v>
+        <v>6433234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
+          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253314</v>
+        <v>120253460</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,35 +1381,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339450</v>
+        <v>339437</v>
       </c>
       <c r="R8" t="n">
-        <v>6433265</v>
+        <v>6433270</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,6 +1450,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120256209</v>
+        <v>120253314</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,31 +1494,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1524,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339403</v>
+        <v>339450</v>
       </c>
       <c r="R9" t="n">
-        <v>6433219</v>
+        <v>6433265</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1562,17 +1572,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1591,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253460</v>
+        <v>120256209</v>
       </c>
       <c r="B10" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,36 +1609,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1640,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339437</v>
+        <v>339403</v>
       </c>
       <c r="R10" t="n">
-        <v>6433270</v>
+        <v>6433219</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,7 +1681,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
+          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,7 +1690,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120253305</v>
+        <v>120256073</v>
       </c>
       <c r="B2" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339460</v>
+        <v>339403</v>
       </c>
       <c r="R2" t="n">
-        <v>6433267</v>
+        <v>6433234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120256522</v>
+        <v>120253460</v>
       </c>
       <c r="B3" t="n">
-        <v>96654</v>
+        <v>5169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,31 +800,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2617</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -879,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120256381</v>
+        <v>120256264</v>
       </c>
       <c r="B4" t="n">
         <v>96198</v>
@@ -942,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -959,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339476</v>
+        <v>339412</v>
       </c>
       <c r="R4" t="n">
-        <v>6433278</v>
+        <v>6433188</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,6 +993,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120255941</v>
+        <v>120253305</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,31 +1037,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339403</v>
+        <v>339460</v>
       </c>
       <c r="R5" t="n">
-        <v>6433234</v>
+        <v>6433267</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1117,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
+          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,6 +1126,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253580</v>
+        <v>120253314</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,35 +1161,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339432</v>
+        <v>339450</v>
       </c>
       <c r="R6" t="n">
-        <v>6433269</v>
+        <v>6433265</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,17 +1235,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120256073</v>
+        <v>120253580</v>
       </c>
       <c r="B7" t="n">
-        <v>5169</v>
+        <v>57689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,28 +1276,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1297,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339403</v>
+        <v>339432</v>
       </c>
       <c r="R7" t="n">
-        <v>6433234</v>
+        <v>6433269</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,7 +1352,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1361,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1365,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253460</v>
+        <v>120256381</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>96198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,32 +1395,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339437</v>
+        <v>339476</v>
       </c>
       <c r="R8" t="n">
-        <v>6433270</v>
+        <v>6433278</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,11 +1467,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120253314</v>
+        <v>120256522</v>
       </c>
       <c r="B9" t="n">
-        <v>96198</v>
+        <v>96654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,20 +1506,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2617</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1515,16 +1527,8 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1534,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339450</v>
+        <v>339437</v>
       </c>
       <c r="R9" t="n">
-        <v>6433265</v>
+        <v>6433270</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,6 +1574,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120256264</v>
+        <v>120255941</v>
       </c>
       <c r="B11" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,39 +1729,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1760,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339412</v>
+        <v>339403</v>
       </c>
       <c r="R11" t="n">
-        <v>6433188</v>
+        <v>6433234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,7 +1801,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
+          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1810,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120256073</v>
+        <v>120255941</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -760,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -905,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120256264</v>
+        <v>120253314</v>
       </c>
       <c r="B4" t="n">
         <v>96198</v>
@@ -940,12 +938,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -957,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339412</v>
+        <v>339450</v>
       </c>
       <c r="R4" t="n">
-        <v>6433188</v>
+        <v>6433265</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,11 +991,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120253305</v>
+        <v>120256073</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,35 +1034,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339460</v>
+        <v>339403</v>
       </c>
       <c r="R5" t="n">
-        <v>6433267</v>
+        <v>6433234</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253314</v>
+        <v>120253305</v>
       </c>
       <c r="B6" t="n">
         <v>96198</v>
@@ -1180,12 +1166,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1197,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339450</v>
+        <v>339460</v>
       </c>
       <c r="R6" t="n">
-        <v>6433265</v>
+        <v>6433267</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,6 +1219,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120253580</v>
+        <v>120256209</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,20 +1263,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1293,18 +1284,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339432</v>
+        <v>339403</v>
       </c>
       <c r="R7" t="n">
-        <v>6433269</v>
+        <v>6433219</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1352,7 +1335,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120256381</v>
+        <v>120256132</v>
       </c>
       <c r="B8" t="n">
         <v>96198</v>
@@ -1414,7 +1397,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1431,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339476</v>
+        <v>339403</v>
       </c>
       <c r="R8" t="n">
-        <v>6433278</v>
+        <v>6433234</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1467,6 +1450,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120256522</v>
+        <v>120256264</v>
       </c>
       <c r="B9" t="n">
-        <v>96654</v>
+        <v>96198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,20 +1494,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2617</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1527,8 +1515,16 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1538,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339437</v>
+        <v>339412</v>
       </c>
       <c r="R9" t="n">
-        <v>6433270</v>
+        <v>6433188</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1578,7 +1574,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1602,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120256209</v>
+        <v>120253580</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,20 +1614,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1639,10 +1635,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1650,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339403</v>
+        <v>339432</v>
       </c>
       <c r="R10" t="n">
-        <v>6433219</v>
+        <v>6433269</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1690,7 +1694,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120255941</v>
+        <v>120256381</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,31 +1733,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1761,10 +1773,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339403</v>
+        <v>339476</v>
       </c>
       <c r="R11" t="n">
-        <v>6433234</v>
+        <v>6433278</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1799,17 +1811,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1828,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120256132</v>
+        <v>120256522</v>
       </c>
       <c r="B12" t="n">
-        <v>96198</v>
+        <v>96654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,20 +1848,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>2617</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1861,16 +1869,8 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R12" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2063,6 +2063,356 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120508146</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skårs, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>339464</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433258</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120508121</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skårs, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>339464</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433258</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120508141</v>
+      </c>
+      <c r="B16" t="n">
+        <v>94344</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skårs, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>339464</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433258</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120255941</v>
+        <v>120256209</v>
       </c>
       <c r="B2" t="n">
         <v>57336</v>
@@ -722,7 +722,7 @@
         <v>339403</v>
       </c>
       <c r="R2" t="n">
-        <v>6433234</v>
+        <v>6433219</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
+          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120253460</v>
+        <v>120255941</v>
       </c>
       <c r="B3" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,36 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339437</v>
+        <v>339403</v>
       </c>
       <c r="R3" t="n">
-        <v>6433270</v>
+        <v>6433234</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
+          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120253314</v>
+        <v>120253460</v>
       </c>
       <c r="B4" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,35 +913,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339450</v>
+        <v>339437</v>
       </c>
       <c r="R4" t="n">
-        <v>6433265</v>
+        <v>6433270</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +982,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120256073</v>
+        <v>120256381</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>96198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,28 +1030,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339403</v>
+        <v>339476</v>
       </c>
       <c r="R5" t="n">
-        <v>6433234</v>
+        <v>6433278</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,11 +1102,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120253305</v>
+        <v>120256264</v>
       </c>
       <c r="B6" t="n">
         <v>96198</v>
@@ -1183,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339460</v>
+        <v>339412</v>
       </c>
       <c r="R6" t="n">
-        <v>6433267</v>
+        <v>6433188</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120256209</v>
+        <v>120256073</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,28 +1261,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1298,7 +1297,7 @@
         <v>339403</v>
       </c>
       <c r="R7" t="n">
-        <v>6433219</v>
+        <v>6433234</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,7 +1334,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1343,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120256132</v>
+        <v>120253580</v>
       </c>
       <c r="B8" t="n">
-        <v>96198</v>
+        <v>57689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,35 +1378,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339403</v>
+        <v>339432</v>
       </c>
       <c r="R8" t="n">
-        <v>6433234</v>
+        <v>6433269</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1463,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1482,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120256264</v>
+        <v>120256132</v>
       </c>
       <c r="B9" t="n">
         <v>96198</v>
@@ -1517,12 +1516,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1534,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339412</v>
+        <v>339403</v>
       </c>
       <c r="R9" t="n">
-        <v>6433188</v>
+        <v>6433234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1574,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
+          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253580</v>
+        <v>120253305</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>96198</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,35 +1617,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1654,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339432</v>
+        <v>339460</v>
       </c>
       <c r="R10" t="n">
-        <v>6433269</v>
+        <v>6433267</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1694,7 +1693,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,6 +1702,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120256381</v>
+        <v>120256522</v>
       </c>
       <c r="B11" t="n">
-        <v>96198</v>
+        <v>96654</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,20 +1733,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>2617</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1754,16 +1754,8 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1773,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339476</v>
+        <v>339437</v>
       </c>
       <c r="R11" t="n">
-        <v>6433278</v>
+        <v>6433270</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1809,6 +1801,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120256522</v>
+        <v>120253314</v>
       </c>
       <c r="B12" t="n">
-        <v>96654</v>
+        <v>96198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,20 +1845,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2617</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1869,8 +1866,16 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1880,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339437</v>
+        <v>339450</v>
       </c>
       <c r="R12" t="n">
-        <v>6433270</v>
+        <v>6433265</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1916,11 +1921,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120508146</v>
+        <v>120508141</v>
       </c>
       <c r="B14" t="n">
-        <v>57336</v>
+        <v>94344</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,31 +2077,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,6 +2163,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2181,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120508121</v>
+        <v>120508146</v>
       </c>
       <c r="B15" t="n">
-        <v>96885</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,31 +2194,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2260,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,7 +2280,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120508141</v>
+        <v>120508121</v>
       </c>
       <c r="B16" t="n">
-        <v>94344</v>
+        <v>96885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,21 +2314,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120256209</v>
+        <v>120253314</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
+        <v>96198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339403</v>
+        <v>339450</v>
       </c>
       <c r="R2" t="n">
-        <v>6433219</v>
+        <v>6433265</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,17 +765,13 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120255941</v>
+        <v>120253580</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +802,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,10 +823,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339403</v>
+        <v>339432</v>
       </c>
       <c r="R3" t="n">
-        <v>6433234</v>
+        <v>6433269</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
+          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120253460</v>
+        <v>120256264</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>96198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,32 +925,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>339437</v>
+        <v>339412</v>
       </c>
       <c r="R4" t="n">
-        <v>6433270</v>
+        <v>6433188</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +1001,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
+          <t>Växte 15 m från reservatsgränsen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1129,7 +1144,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120256264</v>
+        <v>120256132</v>
       </c>
       <c r="B6" t="n">
         <v>96198</v>
@@ -1164,12 +1179,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1181,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>339412</v>
+        <v>339403</v>
       </c>
       <c r="R6" t="n">
-        <v>6433188</v>
+        <v>6433234</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växte 15 m från reservatsgränsen.</t>
+          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120256073</v>
+        <v>120253460</v>
       </c>
       <c r="B7" t="n">
         <v>5169</v>
@@ -1286,7 +1301,11 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1294,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R7" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1353,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Breda (10-15 mm) gnagspår noterades i splintveden hos ett 25 cm tjockt torrträd av gran, nära alkärret. Rutorna på papperet på bilderna är 5 mm breda.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120253580</v>
+        <v>120255941</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,20 +1393,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1395,18 +1414,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>339432</v>
+        <v>339403</v>
       </c>
       <c r="R8" t="n">
-        <v>6433269</v>
+        <v>6433234</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1465,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Litet meståg med 5-6 kungsfåglar i kanten på alkärret.</t>
+          <t>Högstubbe med spillkråkehack, relativt färska spår.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120256132</v>
+        <v>120256522</v>
       </c>
       <c r="B9" t="n">
-        <v>96198</v>
+        <v>96654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,20 +1504,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2617</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1514,16 +1525,8 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1533,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R9" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,7 +1576,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Invid en högstubbe av gran, i vilken det fanns spår av både spillkråkans födosök och bronshjonens gnag.</t>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120253305</v>
+        <v>120256073</v>
       </c>
       <c r="B10" t="n">
-        <v>96198</v>
+        <v>5169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,35 +1620,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1653,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339460</v>
+        <v>339403</v>
       </c>
       <c r="R10" t="n">
-        <v>6433267</v>
+        <v>6433234</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,7 +1689,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120256522</v>
+        <v>120253305</v>
       </c>
       <c r="B11" t="n">
-        <v>96654</v>
+        <v>96198</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,20 +1729,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2617</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1754,8 +1750,16 @@
           <t>(L.) Gray</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1765,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339437</v>
+        <v>339460</v>
       </c>
       <c r="R11" t="n">
-        <v>6433270</v>
+        <v>6433267</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1805,7 +1809,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>noterades vid denna fläck, men det fanns mer av arten i detta skogsparti.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120253314</v>
+        <v>120256209</v>
       </c>
       <c r="B12" t="n">
-        <v>96198</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,39 +1849,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1885,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339450</v>
+        <v>339403</v>
       </c>
       <c r="R12" t="n">
-        <v>6433265</v>
+        <v>6433219</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1923,13 +1919,17 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillkråkehack vid basen hos ett torrträd av tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120508141</v>
+        <v>120508146</v>
       </c>
       <c r="B14" t="n">
-        <v>94344</v>
+        <v>57336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,31 +2077,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,7 +2163,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2182,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120508146</v>
+        <v>120508121</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,31 +2193,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2261,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,6 +2279,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120508121</v>
+        <v>120508141</v>
       </c>
       <c r="B16" t="n">
-        <v>96885</v>
+        <v>94344</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,21 +2314,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 39592-2024 artfynd.xlsx
+++ b/artfynd/A 39592-2024 artfynd.xlsx
@@ -1492,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120256522</v>
+        <v>120256073</v>
       </c>
       <c r="B9" t="n">
-        <v>96654</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,31 +1504,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2617</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1536,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>339437</v>
+        <v>339403</v>
       </c>
       <c r="R9" t="n">
-        <v>6433270</v>
+        <v>6433234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,7 +1577,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
+          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120256073</v>
+        <v>120256522</v>
       </c>
       <c r="B10" t="n">
-        <v>5169</v>
+        <v>96654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,32 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>2617</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>339403</v>
+        <v>339437</v>
       </c>
       <c r="R10" t="n">
-        <v>6433234</v>
+        <v>6433270</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Breda gnagspår i splintveden på samma granhögstubbe som spillkråkan hackat i.</t>
+          <t>Växte i alkärret några meter ut, där det var en lite naknare fläck med vatten stående. Växte tillsammans med stor fickmossa och bålflikmossa.</t>
         </is>
       </c>
       <c r="AD10" t="b">
